--- a/LvM_fasted.xlsx
+++ b/LvM_fasted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/boyuan/Desktop/Harvard/Research/Energy Metabolism Atlas/LvM_Fasted/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE750485-F277-9341-BC22-71A97DA30BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DC655B-EBB5-E141-94B9-467C02FD7DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{5E0D7404-E754-4442-97F6-BA3E5E250F0E}"/>
+    <workbookView xWindow="4080" yWindow="22340" windowWidth="30240" windowHeight="18900" xr2:uid="{5E0D7404-E754-4442-97F6-BA3E5E250F0E}"/>
   </bookViews>
   <sheets>
     <sheet name="LvM" sheetId="37" r:id="rId1"/>
